--- a/総合テスト/会員・ログイン機能/総合テスト会員・ログイン機能項目.xlsx
+++ b/総合テスト/会員・ログイン機能/総合テスト会員・ログイン機能項目.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="6"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="4-1"/>
@@ -94,7 +94,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -126,16 +126,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -442,18 +448,18 @@
   <dimension ref="A1:L42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -468,11 +474,11 @@
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
+      <c r="L1" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="1"/>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>14</v>
       </c>
       <c r="C2" s="1"/>
@@ -484,7 +490,7 @@
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
+      <c r="L2" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="1"/>
@@ -498,7 +504,7 @@
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
+      <c r="L3" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="1"/>
@@ -512,7 +518,7 @@
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
+      <c r="L4" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="1"/>
@@ -526,7 +532,7 @@
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
+      <c r="L5" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="1"/>
@@ -540,7 +546,7 @@
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
+      <c r="L6" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="1"/>
@@ -554,7 +560,7 @@
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
+      <c r="L7" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="1"/>
@@ -568,7 +574,7 @@
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
+      <c r="L8" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="1"/>
@@ -582,7 +588,7 @@
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
+      <c r="L9" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="1"/>
@@ -596,7 +602,7 @@
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
+      <c r="L10" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="1"/>
@@ -610,7 +616,7 @@
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
+      <c r="L11" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="1"/>
@@ -624,7 +630,7 @@
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
+      <c r="L12" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="1"/>
@@ -638,7 +644,7 @@
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
+      <c r="L13" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="1"/>
@@ -652,7 +658,7 @@
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
+      <c r="L14" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="1"/>
@@ -666,7 +672,7 @@
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
+      <c r="L15" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="1"/>
@@ -680,11 +686,11 @@
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
+      <c r="L16" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="1"/>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C17" s="1"/>
@@ -693,12 +699,12 @@
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
-      <c r="I17" s="2" t="s">
+      <c r="I17" s="3" t="s">
         <v>16</v>
       </c>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
-      <c r="L17" s="1"/>
+      <c r="L17" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="1"/>
@@ -712,7 +718,7 @@
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
+      <c r="L18" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="1"/>
@@ -726,7 +732,7 @@
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
+      <c r="L19" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="1"/>
@@ -740,7 +746,7 @@
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
-      <c r="L20" s="1"/>
+      <c r="L20" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="1"/>
@@ -754,7 +760,7 @@
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
-      <c r="L21" s="1"/>
+      <c r="L21" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="1"/>
@@ -768,7 +774,7 @@
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
-      <c r="L22" s="1"/>
+      <c r="L22" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="1"/>
@@ -782,7 +788,7 @@
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
-      <c r="L23" s="1"/>
+      <c r="L23" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="1"/>
@@ -796,7 +802,7 @@
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
+      <c r="L24" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="1"/>
@@ -810,7 +816,7 @@
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
-      <c r="L25" s="1"/>
+      <c r="L25" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="1"/>
@@ -824,7 +830,7 @@
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
-      <c r="L26" s="1"/>
+      <c r="L26" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="1"/>
@@ -838,7 +844,7 @@
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
-      <c r="L27" s="1"/>
+      <c r="L27" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="1"/>
@@ -852,7 +858,7 @@
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
-      <c r="L28" s="1"/>
+      <c r="L28" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="1"/>
@@ -866,7 +872,7 @@
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
-      <c r="L29" s="1"/>
+      <c r="L29" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="1"/>
@@ -880,7 +886,7 @@
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
-      <c r="L30" s="1"/>
+      <c r="L30" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
       <c r="A31" s="1"/>
@@ -894,7 +900,7 @@
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
-      <c r="L31" s="1"/>
+      <c r="L31" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
       <c r="A32" s="1"/>
@@ -908,7 +914,7 @@
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
-      <c r="L32" s="1"/>
+      <c r="L32" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
       <c r="A33" s="1"/>
@@ -922,7 +928,7 @@
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
-      <c r="L33" s="1"/>
+      <c r="L33" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
       <c r="A34" s="1"/>
@@ -936,7 +942,7 @@
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
-      <c r="L34" s="1"/>
+      <c r="L34" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
       <c r="A35" s="1"/>
@@ -950,7 +956,7 @@
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
-      <c r="L35" s="1"/>
+      <c r="L35" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
       <c r="A36" s="1"/>
@@ -964,7 +970,7 @@
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
-      <c r="L36" s="1"/>
+      <c r="L36" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
       <c r="A37" s="1"/>
@@ -978,7 +984,7 @@
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
-      <c r="L37" s="1"/>
+      <c r="L37" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
       <c r="A38" s="1"/>
@@ -992,7 +998,7 @@
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
-      <c r="L38" s="1"/>
+      <c r="L38" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
       <c r="A39" s="1"/>
@@ -1006,7 +1012,7 @@
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
-      <c r="L39" s="1"/>
+      <c r="L39" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
       <c r="A40" s="1"/>
@@ -1020,13 +1026,13 @@
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
-      <c r="L40" s="1"/>
+      <c r="L40" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
-      <c r="D41" s="2" t="s">
+      <c r="D41" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E41" s="1"/>
@@ -1036,7 +1042,7 @@
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
-      <c r="L41" s="1"/>
+      <c r="L41" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
       <c r="A42" s="1"/>
@@ -1050,7 +1056,7 @@
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
-      <c r="L42" s="2" t="s">
+      <c r="L42" s="3" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1067,339 +1073,339 @@
   <dimension ref="A1:B81"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
+      <c r="B1" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
+      <c r="B2" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="1"/>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
+      <c r="B4" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
+      <c r="B5" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
+      <c r="B6" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
+      <c r="B7" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
+      <c r="B8" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
+      <c r="B9" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
+      <c r="B10" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
+      <c r="B11" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
+      <c r="B12" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
+      <c r="B13" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
+      <c r="B14" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
+      <c r="B15" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
+      <c r="B16" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
+      <c r="B17" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
+      <c r="B18" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
+      <c r="B19" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
+      <c r="B20" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
+      <c r="B21" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
+      <c r="B22" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
+      <c r="B23" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
+      <c r="B24" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
+      <c r="B25" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
+      <c r="B26" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
+      <c r="B27" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="1"/>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="1"/>
-      <c r="B29" s="1"/>
+      <c r="B29" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="1"/>
-      <c r="B30" s="1"/>
+      <c r="B30" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
       <c r="A31" s="1"/>
-      <c r="B31" s="1"/>
+      <c r="B31" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
       <c r="A32" s="1"/>
-      <c r="B32" s="1"/>
+      <c r="B32" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
       <c r="A33" s="1"/>
-      <c r="B33" s="1"/>
+      <c r="B33" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
       <c r="A34" s="1"/>
-      <c r="B34" s="1"/>
+      <c r="B34" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
       <c r="A35" s="1"/>
-      <c r="B35" s="1"/>
+      <c r="B35" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
       <c r="A36" s="1"/>
-      <c r="B36" s="1"/>
+      <c r="B36" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
       <c r="A37" s="1"/>
-      <c r="B37" s="1"/>
+      <c r="B37" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
       <c r="A38" s="1"/>
-      <c r="B38" s="1"/>
+      <c r="B38" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
       <c r="A39" s="1"/>
-      <c r="B39" s="1"/>
+      <c r="B39" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
       <c r="A40" s="1"/>
-      <c r="B40" s="1"/>
+      <c r="B40" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
       <c r="A41" s="1"/>
-      <c r="B41" s="1"/>
+      <c r="B41" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
       <c r="A42" s="1"/>
-      <c r="B42" s="1"/>
+      <c r="B42" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
       <c r="A43" s="1"/>
-      <c r="B43" s="1"/>
+      <c r="B43" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
       <c r="A44" s="1"/>
-      <c r="B44" s="1"/>
+      <c r="B44" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
       <c r="A45" s="1"/>
-      <c r="B45" s="1"/>
+      <c r="B45" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
       <c r="A46" s="1"/>
-      <c r="B46" s="1"/>
+      <c r="B46" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
       <c r="A47" s="1"/>
-      <c r="B47" s="1"/>
+      <c r="B47" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
       <c r="A48" s="1"/>
-      <c r="B48" s="1"/>
+      <c r="B48" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
       <c r="A49" s="1"/>
-      <c r="B49" s="1"/>
+      <c r="B49" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
       <c r="A50" s="1"/>
-      <c r="B50" s="1"/>
+      <c r="B50" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
       <c r="A51" s="1"/>
-      <c r="B51" s="2" t="s">
+      <c r="B51" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
       <c r="A52" s="1"/>
-      <c r="B52" s="1"/>
+      <c r="B52" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
       <c r="A53" s="1"/>
-      <c r="B53" s="1"/>
+      <c r="B53" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
       <c r="A54" s="1"/>
-      <c r="B54" s="1"/>
+      <c r="B54" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
       <c r="A55" s="1"/>
-      <c r="B55" s="1"/>
+      <c r="B55" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75">
       <c r="A56" s="1"/>
-      <c r="B56" s="1"/>
+      <c r="B56" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
       <c r="A57" s="1"/>
-      <c r="B57" s="1"/>
+      <c r="B57" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
       <c r="A58" s="1"/>
-      <c r="B58" s="1"/>
+      <c r="B58" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
       <c r="A59" s="1"/>
-      <c r="B59" s="1"/>
+      <c r="B59" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
       <c r="A60" s="1"/>
-      <c r="B60" s="1"/>
+      <c r="B60" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
       <c r="A61" s="1"/>
-      <c r="B61" s="1"/>
+      <c r="B61" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
       <c r="A62" s="1"/>
-      <c r="B62" s="1"/>
+      <c r="B62" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
       <c r="A63" s="1"/>
-      <c r="B63" s="1"/>
+      <c r="B63" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
       <c r="A64" s="1"/>
-      <c r="B64" s="1"/>
+      <c r="B64" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
       <c r="A65" s="1"/>
-      <c r="B65" s="1"/>
+      <c r="B65" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
       <c r="A66" s="1"/>
-      <c r="B66" s="1"/>
+      <c r="B66" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
       <c r="A67" s="1"/>
-      <c r="B67" s="1"/>
+      <c r="B67" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
       <c r="A68" s="1"/>
-      <c r="B68" s="1"/>
+      <c r="B68" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
       <c r="A69" s="1"/>
-      <c r="B69" s="1"/>
+      <c r="B69" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
       <c r="A70" s="1"/>
-      <c r="B70" s="1"/>
+      <c r="B70" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
       <c r="A71" s="1"/>
-      <c r="B71" s="1"/>
+      <c r="B71" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
       <c r="A72" s="1"/>
-      <c r="B72" s="1"/>
+      <c r="B72" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
       <c r="A73" s="1"/>
-      <c r="B73" s="1"/>
+      <c r="B73" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
       <c r="A74" s="1"/>
-      <c r="B74" s="1"/>
+      <c r="B74" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
       <c r="A75" s="1"/>
-      <c r="B75" s="1"/>
+      <c r="B75" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
       <c r="A76" s="1"/>
-      <c r="B76" s="1"/>
+      <c r="B76" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
       <c r="A77" s="1"/>
-      <c r="B77" s="1"/>
+      <c r="B77" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75">
       <c r="A78" s="1"/>
-      <c r="B78" s="1"/>
+      <c r="B78" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
       <c r="A79" s="1"/>
-      <c r="B79" s="1"/>
+      <c r="B79" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">
       <c r="A80" s="1"/>
-      <c r="B80" s="1"/>
+      <c r="B80" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
       <c r="A81" s="1"/>
-      <c r="B81" s="2" t="s">
+      <c r="B81" s="3" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1416,131 +1422,131 @@
   <dimension ref="A1:B30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
+      <c r="B1" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
+      <c r="B2" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="1"/>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
+      <c r="B4" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
+      <c r="B5" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
+      <c r="B6" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
+      <c r="B7" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
+      <c r="B8" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
+      <c r="B9" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
+      <c r="B10" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
+      <c r="B11" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
+      <c r="B12" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
+      <c r="B13" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
+      <c r="B14" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
+      <c r="B15" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
+      <c r="B16" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
+      <c r="B17" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
+      <c r="B18" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
+      <c r="B19" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
+      <c r="B20" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
+      <c r="B21" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
+      <c r="B22" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
+      <c r="B23" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
+      <c r="B24" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
+      <c r="B25" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
+      <c r="B26" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
+      <c r="B27" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="1"/>
-      <c r="B28" s="1"/>
+      <c r="B28" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="1"/>
-      <c r="B29" s="1"/>
+      <c r="B29" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="1"/>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="3" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1557,152 +1563,152 @@
   <dimension ref="A1:C28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
+      <c r="C1" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
+      <c r="C3" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
+      <c r="C4" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
+      <c r="C5" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
+      <c r="C6" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
+      <c r="C7" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
+      <c r="C8" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
+      <c r="C9" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
+      <c r="C10" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
+      <c r="C11" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
+      <c r="C12" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
+      <c r="C13" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
+      <c r="C14" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
+      <c r="C15" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
+      <c r="C16" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
+      <c r="C17" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
+      <c r="C18" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
+      <c r="C19" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
+      <c r="C20" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
+      <c r="C21" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
+      <c r="C22" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
+      <c r="C23" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
+      <c r="C24" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
+      <c r="C25" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
+      <c r="C26" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
+      <c r="C27" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="3" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1719,162 +1725,162 @@
   <dimension ref="A1:C30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
+      <c r="C1" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
+      <c r="C2" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
+      <c r="C4" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
+      <c r="C5" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
+      <c r="C6" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
+      <c r="C7" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
+      <c r="C8" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
+      <c r="C9" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
+      <c r="C10" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
+      <c r="C11" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
+      <c r="C12" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
+      <c r="C13" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
+      <c r="C14" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
+      <c r="C15" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
+      <c r="C16" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
+      <c r="C17" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
+      <c r="C18" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
+      <c r="C19" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
+      <c r="C20" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
+      <c r="C21" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
+      <c r="C22" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
+      <c r="C23" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
+      <c r="C24" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
+      <c r="C25" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
+      <c r="C26" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
+      <c r="C27" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
+      <c r="C28" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
+      <c r="C29" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="3" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1891,213 +1897,213 @@
   <dimension ref="A1:B50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
+      <c r="B1" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="1"/>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
+      <c r="B3" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
+      <c r="B4" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
+      <c r="B5" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
+      <c r="B6" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
+      <c r="B7" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
+      <c r="B8" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
+      <c r="B9" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
+      <c r="B10" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
+      <c r="B11" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
+      <c r="B12" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
+      <c r="B13" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
+      <c r="B14" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
+      <c r="B15" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
+      <c r="B16" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
+      <c r="B17" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
+      <c r="B18" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
+      <c r="B19" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
+      <c r="B20" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
+      <c r="B21" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
+      <c r="B22" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
+      <c r="B23" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
+      <c r="B24" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="1"/>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
+      <c r="B26" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
+      <c r="B27" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="1"/>
-      <c r="B28" s="1"/>
+      <c r="B28" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="1"/>
-      <c r="B29" s="1"/>
+      <c r="B29" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="1"/>
-      <c r="B30" s="1"/>
+      <c r="B30" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
       <c r="A31" s="1"/>
-      <c r="B31" s="1"/>
+      <c r="B31" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
       <c r="A32" s="1"/>
-      <c r="B32" s="1"/>
+      <c r="B32" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
       <c r="A33" s="1"/>
-      <c r="B33" s="1"/>
+      <c r="B33" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
       <c r="A34" s="1"/>
-      <c r="B34" s="1"/>
+      <c r="B34" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
       <c r="A35" s="1"/>
-      <c r="B35" s="1"/>
+      <c r="B35" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
       <c r="A36" s="1"/>
-      <c r="B36" s="1"/>
+      <c r="B36" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
       <c r="A37" s="1"/>
-      <c r="B37" s="1"/>
+      <c r="B37" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
       <c r="A38" s="1"/>
-      <c r="B38" s="1"/>
+      <c r="B38" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
       <c r="A39" s="1"/>
-      <c r="B39" s="1"/>
+      <c r="B39" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
       <c r="A40" s="1"/>
-      <c r="B40" s="1"/>
+      <c r="B40" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
       <c r="A41" s="1"/>
-      <c r="B41" s="1"/>
+      <c r="B41" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
       <c r="A42" s="1"/>
-      <c r="B42" s="1"/>
+      <c r="B42" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
       <c r="A43" s="1"/>
-      <c r="B43" s="1"/>
+      <c r="B43" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
       <c r="A44" s="1"/>
-      <c r="B44" s="1"/>
+      <c r="B44" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
       <c r="A45" s="1"/>
-      <c r="B45" s="1"/>
+      <c r="B45" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
       <c r="A46" s="1"/>
-      <c r="B46" s="1"/>
+      <c r="B46" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
       <c r="A47" s="1"/>
-      <c r="B47" s="1"/>
+      <c r="B47" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
       <c r="A48" s="1"/>
-      <c r="B48" s="1"/>
+      <c r="B48" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
       <c r="A49" s="1"/>
-      <c r="B49" s="1"/>
+      <c r="B49" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
       <c r="A50" s="1"/>
-      <c r="B50" s="2" t="s">
+      <c r="B50" s="3" t="s">
         <v>3</v>
       </c>
     </row>
@@ -2114,21 +2120,21 @@
   <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
+      <c r="B1" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="20.25">
+      <c r="B2" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="21.75">
       <c r="A3" s="1"/>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>0</v>
       </c>
     </row>
